--- a/results/regression_output/full_sample_covid_analysis/year_by_year_elasticities.xlsx
+++ b/results/regression_output/full_sample_covid_analysis/year_by_year_elasticities.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,27 +417,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>eu_elasticity</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eap_elasticity</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>eu_pval</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>eap_pval</t>
         </is>
@@ -460,16 +448,16 @@
         <v>2015</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1969972417074853</v>
+        <v>-0.1441995183761592</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0679098301584975</v>
+        <v>-0.1008083521226749</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007333596101021911</v>
+        <v>0.0005852044664456102</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5966924930050528</v>
+        <v>0.1447806164056988</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +465,16 @@
         <v>2016</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.150383235402632</v>
+        <v>-0.09638685000922381</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.05074991238837528</v>
+        <v>-0.08245383755978911</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04123632573682046</v>
+        <v>0.01053358427276208</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6893768540600616</v>
+        <v>0.2296955635163023</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +482,16 @@
         <v>2017</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.1210898959064495</v>
+        <v>-0.07049781266329602</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.02358839608780969</v>
+        <v>-0.04977630836529245</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1138618076453961</v>
+        <v>0.03075177182463928</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8527454274715329</v>
+        <v>0.4721526593606222</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +499,16 @@
         <v>2018</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.09457355120505184</v>
+        <v>-0.05160559104266491</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01676370320699422</v>
+        <v>-0.01192504709120223</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2706496296271212</v>
+        <v>0.09525128968769825</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9001644596058536</v>
+        <v>0.8832575287689512</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +516,16 @@
         <v>2019</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.1035538481021118</v>
+        <v>-0.06098266259276201</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05397111061650986</v>
+        <v>0.03008371447452715</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1860626665711735</v>
+        <v>0.01628263991755663</v>
       </c>
       <c r="E6" t="n">
-        <v>0.676129881097693</v>
+        <v>0.6905695311340545</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +533,16 @@
         <v>2020</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.01031775344356181</v>
+        <v>0.03538154854331732</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1760514993894596</v>
+        <v>0.151983469802256</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8964587374380151</v>
+        <v>0.2383765399874709</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1816055966128087</v>
+        <v>0.07128326347952862</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +550,16 @@
         <v>2021</v>
       </c>
       <c r="B8" t="n">
-        <v>0.04627428619783211</v>
+        <v>0.07828238610506341</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2157702970328599</v>
+        <v>0.1881156387600379</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5611360909097667</v>
+        <v>0.05185843425623338</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1027653343427883</v>
+        <v>0.02050059717718167</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +567,16 @@
         <v>2022</v>
       </c>
       <c r="B9" t="n">
-        <v>0.08170286733497242</v>
+        <v>0.1163135599610463</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2176506800678003</v>
+        <v>0.2003188809679561</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2847732875735052</v>
+        <v>0.02245164531159571</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1072552494485206</v>
+        <v>0.01074895483139504</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +584,16 @@
         <v>2023</v>
       </c>
       <c r="B10" t="n">
-        <v>0.09256064433193065</v>
+        <v>0.1183057333605814</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2732503245077134</v>
+        <v>0.2531911445991303</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2493473483832964</v>
+        <v>0.05571043461746839</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0549686702116341</v>
+        <v>0.00192865551583643</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +601,16 @@
         <v>2024</v>
       </c>
       <c r="B11" t="n">
-        <v>0.08401012521311088</v>
+        <v>0.09462087394906768</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3079344458618531</v>
+        <v>0.2822824401047197</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3129485783537456</v>
+        <v>0.1751048742237318</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03686996130385234</v>
+        <v>0.0006937780809579408</v>
       </c>
     </row>
   </sheetData>
